--- a/data/testscript.xlsx
+++ b/data/testscript.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Madhav\Qspider\Automation\demoWebShop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166853E3-F66F-469C-B282-5F1E39B34451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF17AE8-CD23-45B7-A9A2-E179E66E8F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EE00CF69-BA90-480E-9CC7-8E2FCC20D5AB}"/>
+    <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{EE00CF69-BA90-480E-9CC7-8E2FCC20D5AB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="moveToWishlist" sheetId="2" r:id="rId1"/>
+    <sheet name="Address" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,12 +34,231 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
+  <si>
+    <t>Sl N0</t>
+  </si>
+  <si>
+    <t>RecipientName</t>
+  </si>
+  <si>
+    <t>Recipient Email</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Krishna</t>
+  </si>
+  <si>
+    <t>krishna@gmail.com</t>
+  </si>
+  <si>
+    <t>The Great in the World</t>
+  </si>
+  <si>
+    <t>Madhav Kumar</t>
+  </si>
+  <si>
+    <t>madhav.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>Welcome to our application</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>priya.sharma@yahoo.com</t>
+  </si>
+  <si>
+    <t>Have a wonderful day</t>
+  </si>
+  <si>
+    <t>Rahul Verma</t>
+  </si>
+  <si>
+    <t>rahul.verma@outlook.com</t>
+  </si>
+  <si>
+    <t>Testing email functionality</t>
+  </si>
+  <si>
+    <t>Anjali Singh</t>
+  </si>
+  <si>
+    <t>anjali.singh@gmail.com</t>
+  </si>
+  <si>
+    <t>Thank you for your support</t>
+  </si>
+  <si>
+    <t>Amit Patel</t>
+  </si>
+  <si>
+    <t>amit.patel@company.com</t>
+  </si>
+  <si>
+    <t>Please review the attached document</t>
+  </si>
+  <si>
+    <t>Sneha Gupta</t>
+  </si>
+  <si>
+    <t>sneha.gupta@gmail.com</t>
+  </si>
+  <si>
+    <t>Automation testing is interesting</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>StateIndex</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Address1</t>
+  </si>
+  <si>
+    <t>Address2</t>
+  </si>
+  <si>
+    <t>ZipCode</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>FaxNumber</t>
+  </si>
+  <si>
+    <t>Sri</t>
+  </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>ram101@gmail.com</t>
+  </si>
+  <si>
+    <t>ABC Ltd</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Patna</t>
+  </si>
+  <si>
+    <t>Rajendra Nagar</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>XYZ Ltd</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Noida</t>
+  </si>
+  <si>
+    <t>Sector 62</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>848214</t>
+  </si>
+  <si>
+    <t>201301</t>
+  </si>
+  <si>
+    <t>9124734489</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>8797</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -58,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,15 +286,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -387,11 +641,268 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6828B64B-4B8F-4B94-A025-B72A81370770}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="32.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C02985-16D0-42CF-AD4D-C77A9078A126}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" customWidth="1"/>
+    <col min="7" max="7" width="10.6328125" customWidth="1"/>
+    <col min="8" max="8" width="11.81640625" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" customWidth="1"/>
+    <col min="11" max="11" width="16.1796875" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="mailto:ram101@gmail.com" xr:uid="{8B49E66D-994C-4676-9B83-5BD595AD17C6}"/>
+    <hyperlink ref="C3" r:id="rId2" display="mailto:krishna@gmail.com" xr:uid="{B4D95076-2257-46C4-98D6-8D1E2D3BD0D5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/testscript.xlsx
+++ b/data/testscript.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Madhav\Qspider\Automation\demoWebShop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF17AE8-CD23-45B7-A9A2-E179E66E8F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A74C9A-E80A-4947-85BA-A4ED31E39F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{EE00CF69-BA90-480E-9CC7-8E2FCC20D5AB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EE00CF69-BA90-480E-9CC7-8E2FCC20D5AB}"/>
   </bookViews>
   <sheets>
     <sheet name="moveToWishlist" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="66">
   <si>
     <t>Sl N0</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>1234</t>
+  </si>
+  <si>
+    <t>Confirmation Message</t>
+  </si>
+  <si>
+    <t>The product has been added to your wishlist</t>
   </si>
 </sst>
 </file>
@@ -641,15 +647,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6828B64B-4B8F-4B94-A025-B72A81370770}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="28.1796875" customWidth="1"/>
     <col min="4" max="4" width="32.36328125" customWidth="1"/>
+    <col min="5" max="5" width="39.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -662,8 +669,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -676,8 +686,11 @@
       <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -690,8 +703,11 @@
       <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E3" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -704,8 +720,11 @@
       <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -718,8 +737,11 @@
       <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -732,8 +754,11 @@
       <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E6" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
@@ -746,8 +771,11 @@
       <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E7" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -759,6 +787,9 @@
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
